--- a/TestData/ExampleData.xlsx
+++ b/TestData/ExampleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MaestroLab\Maestro-Excel-Data-Driven-Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7153EB-D6CE-4FB3-87D9-FC72F6748053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBA394D-8258-4C98-851F-E7264EAB3953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="878" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="878" activeTab="1" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
   </bookViews>
   <sheets>
     <sheet name="Example_LoginData" sheetId="12" r:id="rId1"/>

--- a/TestData/ExampleData.xlsx
+++ b/TestData/ExampleData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MaestroLab\Maestro-Excel-Data-Driven-Framework\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohai\AppData\Local\Programs\Maestro Studio\Maestro\Test\Maestro-Excel-Data-Driven-Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBA394D-8258-4C98-851F-E7264EAB3953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96728D42-D4AF-4724-9159-21E9EDC292EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="878" activeTab="1" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="878" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
   </bookViews>
   <sheets>
     <sheet name="Example_LoginData" sheetId="12" r:id="rId1"/>

--- a/TestData/ExampleData.xlsx
+++ b/TestData/ExampleData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohai\AppData\Local\Programs\Maestro Studio\Maestro\Test\Maestro-Excel-Data-Driven-Framework\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohai\AppData\Local\Programs\Maestro Studio\Maestro\Maestro-Excel-Data-Driven-Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96728D42-D4AF-4724-9159-21E9EDC292EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC3D9D6-EB8F-4278-9038-38CCFE88A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="878" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7270" tabRatio="878" activeTab="1" xr2:uid="{8F7D7BB0-42BA-4985-9199-EDA16EBB489C}"/>
   </bookViews>
   <sheets>
     <sheet name="Example_LoginData" sheetId="12" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Username</t>
   </si>
@@ -40,31 +40,7 @@
     <t>example_1</t>
   </si>
   <si>
-    <t>example_4</t>
-  </si>
-  <si>
-    <t>example_5</t>
-  </si>
-  <si>
-    <t>example_6</t>
-  </si>
-  <si>
-    <t>example_7</t>
-  </si>
-  <si>
-    <t>example_8</t>
-  </si>
-  <si>
-    <t>example_9</t>
-  </si>
-  <si>
-    <t>example_10</t>
-  </si>
-  <si>
     <t>example_2</t>
-  </si>
-  <si>
-    <t>example_3</t>
   </si>
 </sst>
 </file>
@@ -516,99 +492,51 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>12346</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>12347</v>
-      </c>
+      <c r="A4" s="6"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12348</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12349</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12350</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
-        <v>12351</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>12352</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12353</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12354</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -650,103 +578,49 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1">
-        <v>12346</v>
-      </c>
+      <c r="A3" s="6"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>12347</v>
-      </c>
+      <c r="A4" s="6"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12348</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12349</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12350</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
-        <v>12351</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>12352</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12353</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12354</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
